--- a/tests/fixtures/public_entities.xlsx
+++ b/tests/fixtures/public_entities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,50 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4331040</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>24079711</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MADE UP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Orasul Zlatna</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Alba, Orasul Zlatna, STRADA PIATA UNIRII, Numar 1A, Bloc/Scara , Sector , Cod postal 5161100</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4331032</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
